--- a/data/credit_bond_all_2026-09-14.xlsx
+++ b/data/credit_bond_all_2026-09-14.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -700,7 +700,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683618.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>5+2+2+1</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9300/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -920,7 +924,11 @@
           <t>09-15 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683624.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -959,7 +967,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1144,7 +1152,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>012682250.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>0.33Y</t>
@@ -1183,7 +1195,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4800/1.4600</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1364,7 +1376,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>102683621.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1403,7 +1419,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/1.6600</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1588,7 +1604,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>012682252.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>0.27Y</t>
@@ -1627,7 +1647,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1808,7 +1828,11 @@
           <t>09-15 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102683625.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1847,7 +1871,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2028,7 +2052,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>102683619.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2067,7 +2095,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2248,7 +2276,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683622.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2287,7 +2319,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2468,7 +2500,11 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>012682242.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -2507,7 +2543,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/1.4900</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2731,7 +2767,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -3415,7 +3451,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6700</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3639,7 +3675,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3861,7 +3897,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4750/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -4081,7 +4117,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9300</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -5201,7 +5237,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0400/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5421,7 +5457,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0400</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5461,7 +5497,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
@@ -5586,7 +5626,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26秦皇城投PPN002</t>
+          <t>26创鸿资产PPN001</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5597,38 +5637,38 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>1.65</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25秦发02</t>
+          <t>25创鸿06</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.47Y</t>
+          <t>4.25Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.8771</t>
+          <t>1.9151</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5638,12 +5678,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司</t>
+          <t>江苏创鸿资产管理有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 11.63</t>
+          <t>C+ 30.06</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5653,7 +5693,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5670,12 +5710,12 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5686,17 +5726,17 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>河北省-秦皇岛市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本次发行6.50亿元,全部用于偿还到期债务融资工具本金；本期发行5.00亿元,全部用于偿还到期债务融资工具本金[25秦皇城投CP002,24秦皇城投PPN001]</t>
+          <t>本期定向债务融资工具注册金额1.65亿元,本期发行金额1.65亿元,拟用于偿还发行人有息债务[26创鸿资产SCP001]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,中国民生银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5717,7 +5757,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>江苏创鸿资产管理有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5727,14 +5767,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -5742,7 +5778,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5752,32 +5788,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5810,7 +5846,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26淮交03</t>
+          <t>26港发04</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5820,43 +5856,43 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>283875.SH</t>
+          <t>283960.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.1</v>
+        <v>3.04</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.20</t>
+          <t>2.10 ~ 3.10</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24淮交02</t>
+          <t>26防城港发PPN001A</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>3.12Y</t>
+          <t>4.45Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7667</t>
+          <t>2.3436</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5866,12 +5902,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司</t>
+          <t>防城港市港发控股集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C 27.85</t>
+          <t>C- 11.40</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5881,7 +5917,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-14 16:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -5898,33 +5934,33 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.43%~2.53%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广西壮族自治区-防城港市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过10.10亿元(含10.10亿元)，发行人拟将本期债券募集资金扣除发行费用后，全部用于偿还公司债券本金[25淮交D2]</t>
+          <t>本期债券募集资金扣除发行费用后拟用于偿还到期公司债券本金[21港发02]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -5945,7 +5981,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>防城港市港发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -5955,14 +5991,10 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-16</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5985,22 +6017,22 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
@@ -6038,7 +6070,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN017</t>
+          <t>26秦皇城投PPN002</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6049,53 +6081,53 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.93</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>25秦发02</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.98Y</t>
+          <t>3.47Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.9747</t>
+          <t>1.8771</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2.0000/--</t>
+          <t>2.0900/1.8500</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>秦皇岛城市发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 37.89</t>
+          <t>C- 11.63</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6122,39 +6154,39 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>河北省-秦皇岛市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>本次发行6.50亿元,全部用于偿还到期债务融资工具本金；本期发行5.00亿元,全部用于偿还到期债务融资工具本金[25秦皇城投CP002,24秦皇城投PPN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国银河证券股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6169,20 +6201,24 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十七期中期票据</t>
+          <t>秦皇岛城市发展投资控股集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -6190,7 +6226,7 @@
       </c>
       <c r="AM27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN27" s="3" t="inlineStr">
@@ -6200,32 +6236,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6258,7 +6294,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业GN0011(科创债)</t>
+          <t>26淮交03</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6266,56 +6302,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>283875.SH</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>10.1</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.20</t>
+          <t>1.30 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业MTN007(科创债)</t>
+          <t>24淮交02</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.74Y</t>
+          <t>3.12Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.1647</t>
+          <t>1.7667</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7400</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司</t>
+          <t>淮安市交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 40.84</t>
+          <t>C 27.85</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6325,7 +6365,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 16:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6335,96 +6375,96 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>华友钴业本期绿色科技创新债券拟发行规模为10.00亿元人民币,募集资金全部用于置换发行人下属公司三个月内用于废旧动力蓄电池及其拆解物回收,以及用于电池级锂盐产品制造项目原材料采购的采购支出,其中22,801.28万元用于置换发行人下属公司衢州华友资源再生科技有限公司三个月内废旧动力蓄电池及其拆解物回收的采购支出;77,198.72万元用于置换发行人下属子公司广西华友锂业有限公司三个月内用于电池级锂盐产品制造项目原材料采购的采购支出</t>
+          <t>本期债券发行规模不超过10.10亿元(含10.10亿元)，发行人拟将本期债券募集资金扣除发行费用后，全部用于偿还公司债券本金[25淮交D2]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,招商银行股份有限公司,中银国际证券股份有限公司,中国银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司2026年度第十一期绿色科技创新债券</t>
+          <t>淮安市交通控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2028-09-15</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2029-09-16</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6434,22 +6474,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6482,7 +6522,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26招商租赁SCP008</t>
+          <t>26晋能煤业MTN017</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6490,56 +6530,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>102683620.IB</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 1.93</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25招商租赁MTN001(绿色)</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>286D</t>
+          <t>4.98Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.5330</t>
+          <t>1.9747</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/1.9500</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>招商局融资租赁有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 27.41</t>
+          <t>B- 37.89</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6549,7 +6593,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6566,12 +6610,12 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6582,28 +6626,28 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,期限为269天。根据发行人资金需求计划,本期超短期融资券募集资金拟用于偿还发行人到期债务融资工具[26招商租赁SCP001]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6613,7 +6657,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>招商局融资租赁有限公司2026年度第八期超短期融资券</t>
+          <t>晋能控股煤业集团有限公司2026年度第十七期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6623,7 +6667,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-06-11</t>
+          <t>2031-09-15</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6644,7 +6688,7 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
@@ -6654,22 +6698,22 @@
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6702,7 +6746,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP019</t>
+          <t>26华友钴业GN011(科创债)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6710,56 +6754,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>132680096.IB</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.80 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26华友钴业MTN007(科创债)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>1.74Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>2.1647</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1800</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>浙江华友钴业股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.65</t>
+          <t>B- 40.84</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6786,12 +6834,12 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6799,31 +6847,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>华友钴业本期绿色科技创新债券拟发行规模为10.00亿元人民币,募集资金全部用于置换发行人下属公司三个月内用于废旧动力蓄电池及其拆解物回收,以及用于电池级锂盐产品制造项目原材料采购的采购支出,其中22,801.28万元用于置换发行人下属公司衢州华友资源再生科技有限公司三个月内废旧动力蓄电池及其拆解物回收的采购支出;77,198.72万元用于置换发行人下属子公司广西华友锂业有限公司三个月内用于电池级锂盐产品制造项目原材料采购的采购支出</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,招商银行股份有限公司,中银国际证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -6833,7 +6885,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十九期超短期融资券</t>
+          <t>浙江华友钴业股份有限公司2026年度第十一期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6843,7 +6895,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2028-09-15</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -6874,22 +6926,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6922,27 +6974,31 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26国网租赁CP009</t>
+          <t>26招商租赁SCP008</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-14 12:00</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>012682249.IB</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.85Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.53</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H31" s="3"/>
@@ -6954,12 +7010,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25国网租赁MTN005(绿色)</t>
+          <t>25招商租赁MTN001(绿色)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>312D</t>
+          <t>286D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -6974,12 +7030,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>国网国际融资租赁有限公司</t>
+          <t>招商局融资租赁有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>C 27.41</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6999,19 +7055,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7027,18 +7083,18 @@
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行规模10亿元，全部用于偿还存量债务融资工具[26国网租赁SCP003]</t>
+          <t>本期超短期融资券发行金额5亿元,期限为269天。根据发行人资金需求计划,本期超短期融资券募集资金拟用于偿还发行人到期债务融资工具[26招商租赁SCP001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,渤海银行股份有限公司</t>
+          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7053,7 +7109,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>国网国际融资租赁有限公司2026年度第九期短期融资券</t>
+          <t>招商局融资租赁有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7063,88 +7119,86 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2027-07-22</t>
+          <t>2027-06-11</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY31" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW31" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX31" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AZ31" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ31" s="3"/>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26深能源SCP003</t>
+          <t>26苏农垦SCP019</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7152,56 +7206,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>012682246.IB</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.60</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26深能源SCP001</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>95D</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.4800</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 42.23</t>
+          <t>C+ 32.65</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7228,12 +7286,12 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7244,17 +7302,17 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金10亿元,其中4.2亿元拟用于偿还发行人有息负债本息,5.8亿元拟用于发行人本部及子公司补充流动资金。</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7275,7 +7333,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司2026年度第三期超短期融资券</t>
+          <t>江苏省农垦集团有限公司2026年度第十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7285,7 +7343,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7311,27 +7369,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7364,18 +7422,22 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26大唐租赁SCP007</t>
+          <t>26国网租赁CP009</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
-        </is>
-      </c>
-      <c r="C33" s="3"/>
+          <t>09-14 12:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>042680313.IB</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>0.85Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -7384,29 +7446,29 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.20 ~ 1.53</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26大唐租赁SCP006</t>
+          <t>25国网租赁MTN005(绿色)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>67D</t>
+          <t>312D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5158</t>
+          <t>1.5330</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7416,12 +7478,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>国网国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>B- 39.08</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7441,19 +7503,23 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7469,18 +7535,18 @@
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为基础发行规模0元，发行金额上限10亿元，用于偿还有息负债[26大唐租赁SCP003]</t>
+          <t>本期短期融资券发行规模10亿元，全部用于偿还存量债务融资工具[26国网租赁SCP003]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>南京银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7495,7 +7561,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>国网国际融资租赁有限公司2026年度第九期短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7505,13 +7571,13 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-07-22</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -7521,7 +7587,7 @@
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
@@ -7531,7 +7597,7 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7579,12 +7645,14 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26河南发电SCP002</t>
+          <t>26深能源SCP003</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7592,56 +7660,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>012682244.IB</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.51Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.20 ~ 1.60</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25河南发电MTN003</t>
+          <t>26深能源SCP001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>332D</t>
+          <t>95D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.5393</t>
+          <t>1.4800</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>大唐河南发电有限公司</t>
+          <t>深圳能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C 27.22</t>
+          <t>B- 42.23</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7668,12 +7740,12 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7684,17 +7756,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期发行超短期融资券5亿元,拟全部用于偿还发行人有息债务[26河南发电SCP001]</t>
+          <t>本期超短期融资券募集资金10亿元,其中4.2亿元拟用于偿还发行人有息负债本息,5.8亿元拟用于发行人本部及子公司补充流动资金。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7705,7 +7777,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -7715,7 +7787,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>大唐河南发电有限公司2026年度第二期超短期融资券</t>
+          <t>深圳能源集团股份有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7725,14 +7797,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -7755,7 +7823,7 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -7765,12 +7833,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -7808,7 +7876,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26平安点创SCP004</t>
+          <t>26大唐租赁SCP007</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7816,56 +7884,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>012682245.IB</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.7Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.70</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26平安点创MTN003</t>
+          <t>26大唐租赁SCP006</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>276D</t>
+          <t>67D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7030</t>
+          <t>1.5158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.4900</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.36</t>
+          <t>C+ 34.80</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7892,12 +7964,12 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.70%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -7908,17 +7980,17 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元。其中3亿元拟用于偿还发行人即将到期的债务融资工具，1亿元拟用于偿还发行人的银行借款。[25平安点创SCP006]</t>
+          <t>本期超短期融资券发行金额为基础发行规模0元，发行金额上限10亿元，用于偿还有息负债[26大唐租赁SCP003]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -7929,7 +8001,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -7939,7 +8011,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司2026年度第四期超短期融资券</t>
+          <t>大唐融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7949,7 +8021,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8023,14 +8095,12 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26山金Y2</t>
+          <t>26河南发电SCP002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8040,12 +8110,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>246069.SH</t>
+          <t>012682243.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.51Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8054,29 +8124,29 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24鲁黄金MTN004(科创票据)</t>
+          <t>25河南发电MTN003</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>223D+N</t>
+          <t>332D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.5603</t>
+          <t>1.5393</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8086,12 +8156,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司</t>
+          <t>大唐河南发电有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.26</t>
+          <t>C 27.22</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8101,7 +8171,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-14 16:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8111,19 +8181,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8134,38 +8204,38 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后拟用于偿还公司有息债务</t>
+          <t>本期发行超短期融资券5亿元,拟全部用于偿还发行人有息债务[26河南发电SCP001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东兴证券股份有限公司,申万宏源证券有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>大唐河南发电有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8175,60 +8245,64 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>火电</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AO36" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR36" s="3" t="inlineStr">
-        <is>
-          <t>有色</t>
-        </is>
-      </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>贵金属</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>黄金</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8236,7 +8310,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8254,49 +8328,53 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26浙交投SCP011</t>
+          <t>26平安点创SCP004</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-14 17:00</t>
-        </is>
-      </c>
-      <c r="C37" s="3"/>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>012682248.IB</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.7Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.23 ~ 1.63</t>
+          <t>1.35 ~ 1.70</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26浙交投SCP010</t>
+          <t>26平安点创MTN003</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>186D</t>
+          <t>276D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.5029</t>
+          <t>1.7030</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8306,12 +8384,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司</t>
+          <t>平安点创国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 44.11</t>
+          <t>D+ 9.36</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8338,12 +8416,12 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.66%~1.70%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8354,17 +8432,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
+          <t>发行人本期超短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元。其中3亿元拟用于偿还发行人即将到期的债务融资工具，1亿元拟用于偿还发行人的银行借款。[25平安点创SCP006]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,广发银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8375,7 +8453,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8385,7 +8463,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司2026年度第十一期超短期融资券</t>
+          <t>平安点创国际融资租赁有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8395,14 +8473,10 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -8420,32 +8494,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8473,12 +8547,14 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP003</t>
+          <t>26山金Y2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8486,56 +8562,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C38" s="3"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>246069.SH</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP002</t>
+          <t>24鲁黄金MTN004(科创票据)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>266D</t>
+          <t>223D+N</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.5303</t>
+          <t>1.5603</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>山东黄金集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 23.34</t>
+          <t>C+ 34.26</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8545,7 +8625,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 16:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8555,50 +8635,46 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后拟用于偿还公司有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,东兴证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8608,12 +8684,12 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期超短期融资券</t>
+          <t>山东黄金集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8623,57 +8699,53 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-16</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>贵金属</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8683,12 +8755,12 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -8706,64 +8778,68 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26福州新发MTN002</t>
+          <t>26浙交投SCP011</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
-        </is>
-      </c>
-      <c r="C39" s="3"/>
+          <t>09-14 17:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>012682247.IB</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.23 ~ 1.63</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24福州新发MTN002</t>
+          <t>26浙交投SCP010</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>186D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6696</t>
+          <t>1.5029</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>福州新区开发投资集团有限公司</t>
+          <t>浙江省交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 10.15</t>
+          <t>B- 44.11</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8773,7 +8849,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-14 10:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8790,12 +8866,12 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -8806,23 +8882,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币6.00亿元,拟用于归还到期债券[21福州新发MTN005]</t>
+          <t>本期超短期融资券募集资金5亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -8837,7 +8913,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>福州新区开发投资集团有限公司2026年度第二期中期票据</t>
+          <t>浙江省交通投资集团有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8847,7 +8923,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t>2027-06-12</t>
         </is>
       </c>
       <c r="AK39" s="3" t="inlineStr">
@@ -8872,12 +8948,12 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
@@ -8887,17 +8963,17 @@
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8925,29 +9001,27 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ39" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ39" s="3"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26亚新煤层气GT02</t>
+          <t>26南京公路SCP003</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-14 17:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>520465.SZ</t>
+          <t>012682251.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -8956,44 +9030,44 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26亚新煤层气GT01</t>
+          <t>26南京公路SCP002</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.60Y</t>
+          <t>266D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.0917</t>
+          <t>1.5303</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.5300</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>新疆亚新煤层气投资开发(集团)有限责任公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 23.34</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9003,7 +9077,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-14 15:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9013,19 +9087,19 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9036,27 +9110,27 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金不超过3.00亿元(含),扣除发行费用后,拟全部用于置换本期债券发行前三个月在低碳转型领域自有资金的支出</t>
+          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>湘财证券股份有限公司</t>
+          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3" t="inlineStr">
         <is>
-          <t>陕西信用增进投资股份有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9066,28 +9140,32 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>新疆亚新煤层气投资开发(集团)有限责任公司2026年面向专业投资者非公开发行低碳转型公司债券(第二期)</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9097,37 +9175,37 @@
       </c>
       <c r="AN40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>油气开采</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9160,7 +9238,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26济轨02</t>
+          <t>26福州新发MTN002</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9170,58 +9248,58 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283995.SH</t>
+          <t>102683623.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26济轨01</t>
+          <t>24福州新发MTN002</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>9.98Y</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.4321</t>
+          <t>1.6696</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6600</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>济南轨道交通集团有限公司</t>
+          <t>福州新区开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.61</t>
+          <t>C- 10.15</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9231,7 +9309,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-14 15:00</t>
+          <t>09-14 10:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9241,7 +9319,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U41" s="3"/>
@@ -9253,7 +9331,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.46%~2.56%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9264,23 +9342,23 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金11亿元扣除发行费用后,拟用于偿还公司债券本金[23济轨03]</t>
+          <t>本期中期票据发行金额为人民币6.00亿元,拟用于归还到期债券[21福州新发MTN005]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中泰证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9290,75 +9368,79 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>济南轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>福州新区开发投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2036-09-16</t>
-        </is>
-      </c>
-      <c r="AK41" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>铁路运输</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9379,73 +9461,75 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26港发03</t>
+          <t>26亚新煤层气GT02</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-14 17:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283959.SH</t>
+          <t>520465.SZ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>3.04</v>
+        <v>3.0</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26防城港发PPN001B</t>
+          <t>26亚新煤层气GT01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.45Y+2.00Y</t>
+          <t>4.60Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.0830</t>
+          <t>2.0917</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>防城港市港发控股集团有限公司</t>
+          <t>新疆亚新煤层气投资开发(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 11.40</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9472,36 +9556,40 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.70%~2.80%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-防城港市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后拟用于偿还到期公司债券本金[21港发02]</t>
+          <t>本期公司债券募集资金不超过3.00亿元(含),扣除发行费用后,拟全部用于置换本期债券发行前三个月在低碳转型领域自有资金的支出</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3"/>
+          <t>湘财证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>陕西信用增进投资股份有限公司</t>
+        </is>
+      </c>
       <c r="AE42" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9514,12 +9602,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>防城港市港发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
+          <t>新疆亚新煤层气投资开发(集团)有限责任公司2026年面向专业投资者非公开发行低碳转型公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9550,47 +9638,47 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>油气开采</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9608,7 +9696,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26港发04</t>
+          <t>26济轨02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9618,58 +9706,58 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283960.SH</t>
+          <t>283995.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3.04</v>
+        <v>11.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 3.10</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26防城港发PPN001B</t>
+          <t>26济轨01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.45Y+2.00Y</t>
+          <t>9.98Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.0830</t>
+          <t>2.4321</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.4200/2.4000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>防城港市港发控股集团有限公司</t>
+          <t>济南轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 11.40</t>
+          <t>C+ 30.61</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9696,33 +9784,33 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.43%~2.53%</t>
+          <t>2.46%~2.56%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-防城港市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后拟用于偿还到期公司债券本金[21港发02]</t>
+          <t>本期债券募集资金11亿元扣除发行费用后,拟用于偿还公司债券本金[23济轨03]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中泰证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -9743,7 +9831,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>防城港市港发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
+          <t>济南轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9753,7 +9841,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
+          <t>2036-09-16</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9774,37 +9862,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -9814,7 +9902,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9832,7 +9920,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>G26垦利1</t>
+          <t>26港发03</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9842,94 +9930,114 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283997.SH</t>
+          <t>283959.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.7</v>
+        <v>3.04</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>26防城港发PPN001B</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>2.45Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2.0830</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>防城港市港发控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>C- 11.40</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>东营市垦利区城市发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>09-14 15:00</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>2.70%~2.80%</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>山东省-东营市</t>
+          <t>广西壮族自治区-防城港市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
+          <t>本期债券募集资金扣除发行费用后拟用于偿还到期公司债券本金[21港发02]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>粤开证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>湖南财鑫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9947,7 +10055,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种一)</t>
+          <t>防城港市港发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9957,7 +10065,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
+          <t>2031-09-16</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -9973,15 +10081,19 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP44" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -9999,22 +10111,22 @@
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-16</t>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10032,7 +10144,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>G26垦利2</t>
+          <t>G26垦利1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10042,12 +10154,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>283998.SH</t>
+          <t>283997.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -10056,7 +10168,7 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H45" s="3"/>
@@ -10107,7 +10219,11 @@
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>2.29%~2.39%</t>
+        </is>
+      </c>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -10147,7 +10263,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种二)</t>
+          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10157,7 +10273,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2033-09-15</t>
+          <t>2031-09-15</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10232,7 +10348,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26吉安井开PPN001A</t>
+          <t>G26垦利2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10240,41 +10356,37 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>283998.SH</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>25吉安井开PPN001</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>2.11Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2.0555</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -10284,14 +10396,10 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>C- 19.58</t>
-        </is>
-      </c>
+          <t>东营市垦利区城市发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -10299,7 +10407,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10314,41 +10422,37 @@
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
+      <c r="W46" s="3"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>2.59%~2.69%</t>
+        </is>
+      </c>
+      <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>山东省-东营市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
+          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>粤开证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10358,12 +10462,12 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种一)</t>
+          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10373,13 +10477,13 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
+          <t>2033-09-15</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
@@ -10394,47 +10498,43 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP46" s="3"/>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10452,7 +10552,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26吉安井开PPN001B</t>
+          <t>26吉安井开PPN001A</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10463,7 +10563,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -10472,14 +10572,14 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -10499,7 +10599,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -10541,7 +10641,7 @@
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -10583,7 +10683,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10644,7 +10744,7 @@
       </c>
       <c r="AU47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AV47" s="3" t="inlineStr">
@@ -10654,7 +10754,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -10667,12 +10767,14 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ47" s="3"/>
+      <c r="AZ47" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN003</t>
+          <t>26吉安井开PPN001B</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10683,53 +10785,53 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>20.0</v>
+        <v>1.8</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN002</t>
+          <t>25吉安井开PPN001</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>2.11Y+2.00Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>2.0555</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 41.25</t>
+          <t>C- 19.58</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10739,7 +10841,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10756,146 +10858,1736 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,中国银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr">
+        <is>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
+        </is>
+      </c>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ48" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="49" customHeight="true" ht="18.0">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>26中冶MTN003</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>102683617.IB</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>26中冶MTN002</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>2.95Y+N</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>1.7587</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>1.7600/--</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>中国冶金科工股份有限公司</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>B- 41.25</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>09-14 09:00</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司,中国银行股份有限公司,中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
           <t>中期票据</t>
         </is>
       </c>
-      <c r="AF48" s="3" t="inlineStr">
+      <c r="AF49" s="3" t="inlineStr">
         <is>
           <t>国有企业</t>
         </is>
       </c>
-      <c r="AG48" s="3" t="inlineStr">
+      <c r="AG49" s="3" t="inlineStr">
         <is>
           <t>银行间</t>
         </is>
       </c>
-      <c r="AH48" s="3" t="inlineStr">
+      <c r="AH49" s="3" t="inlineStr">
         <is>
           <t>中国冶金科工股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
-      <c r="AI48" s="3" t="inlineStr">
+      <c r="AI49" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AJ48" s="3" t="inlineStr">
+      <c r="AJ49" s="3" t="inlineStr">
         <is>
           <t>2029-09-15</t>
         </is>
       </c>
-      <c r="AK48" s="3" t="inlineStr">
+      <c r="AK49" s="3" t="inlineStr">
         <is>
           <t>休2</t>
         </is>
       </c>
-      <c r="AL48" s="3" t="inlineStr">
+      <c r="AL49" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
+      <c r="AM49" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
+      <c r="AN49" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AO48" s="3" t="inlineStr">
+      <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
+      <c r="AP49" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AQ48" s="3" t="inlineStr">
+      <c r="AQ49" s="3" t="inlineStr">
         <is>
           <t>建筑施工</t>
         </is>
       </c>
-      <c r="AR48" s="3" t="inlineStr">
+      <c r="AR49" s="3" t="inlineStr">
         <is>
           <t>综合建筑施工</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AS49" s="3" t="inlineStr">
         <is>
           <t>综合建筑施工</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
+      <c r="AT49" s="3" t="inlineStr">
         <is>
           <t>专业工程</t>
         </is>
       </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AU49" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
+      <c r="AV49" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW48" s="3" t="inlineStr">
+      <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>永续</t>
         </is>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
+      <c r="AX49" s="3" t="inlineStr">
         <is>
           <t>次级债权</t>
         </is>
       </c>
-      <c r="AY48" s="3" t="inlineStr">
+      <c r="AY49" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ48" s="3"/>
+      <c r="AZ49" s="3"/>
+    </row>
+    <row r="50" customHeight="true" ht="18.0">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>26商古02</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>283965.SH</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>24商古06</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>2.72Y</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>1.8619</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>1.8800/1.8300</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>商丘市古城保护开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>B- 43.66</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>09-14 16:00</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>河南省-商丘市</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[25商古D5,25商古D6]</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>申万宏源证券有限公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr">
+        <is>
+          <t>商丘市发展投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr">
+        <is>
+          <t>商丘市古城保护开发建设有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK50" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ50" s="3"/>
+    </row>
+    <row r="51" customHeight="true" ht="18.0">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>26枣新02</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>09-14 17:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>284007.SH</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.10</t>
+        </is>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>26枣新01</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>4.64Y</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>2.1722</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>枣庄高新投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>B- 37.94</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>2.16%~2.26%</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>山东省-枣庄市</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于回售“23枣新02”公司债券。[23 枣新02]</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>申港证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr">
+        <is>
+          <t>枣庄高新投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK51" s="3"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ51" s="3"/>
+    </row>
+    <row r="52" customHeight="true" ht="18.0">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>26融运01</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>284032.SH</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>25融运01</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2.19Y</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1.8849</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>--/1.8000</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>新乡新融资产运营有限公司</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>C 30.00</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>09-14 16:00</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>河南省-新乡市</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司到期有息债务。</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr">
+        <is>
+          <t>新乡新融资产运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-16</t>
+        </is>
+      </c>
+      <c r="AK52" s="3"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ52" s="3"/>
+    </row>
+    <row r="53" customHeight="true" ht="18.0">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>HDGJYK02</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>246092.SH</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2+N</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>HDGJYK01</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>1.87Y+N</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>1.5926</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>1.6000/--</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>华电国际电力股份有限公司</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.31</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr">
+        <is>
+          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
+        </is>
+      </c>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr">
+        <is>
+          <t>2028-09-16</t>
+        </is>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>火电</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ53" s="3"/>
+    </row>
+    <row r="54" customHeight="true" ht="18.0">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>HDGJYK03</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>246093.SH</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>HDGJYK01</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>1.87Y+N</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>1.5926</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>1.6000/--</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>华电国际电力股份有限公司</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.31</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr">
+        <is>
+          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
+        </is>
+      </c>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-16</t>
+        </is>
+      </c>
+      <c r="AK54" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>火电</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ54" s="3"/>
+    </row>
+    <row r="55" customHeight="true" ht="18.0">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>GZ国保01</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>246085.SH</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>26国保03</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>1.74Y</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>1.6593</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>1.7100/--</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>国新商业保理有限公司</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.17</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金拟将2.00亿元用于置换发行前3个月以内通过自有资金向中小微企业投放的保理融资款</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,国新证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>国新商业保理有限公司2026年面向专业投资者公开发行绿色中小微企业支持债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr">
+        <is>
+          <t>2028-09-16</t>
+        </is>
+      </c>
+      <c r="AK55" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AZ55" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-14.xlsx
+++ b/data/credit_bond_all_2026-09-14.xlsx
@@ -721,8 +721,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>19.12</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -975,7 +979,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1181,8 +1185,12 @@
           <t>1.30 ~ 1.50</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>21.56</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.43</t>
@@ -1402,15 +1410,19 @@
         <v>5.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.34 ~ 1.64</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>39.09</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -1643,8 +1655,12 @@
           <t>1.20 ~ 1.48</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>12.56</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -1897,7 +1913,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2099,8 +2115,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>35.09</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -2322,15 +2342,19 @@
         <v>20.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.49 ~ 1.79</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>37.11</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.79</t>
@@ -2555,8 +2579,12 @@
           <t>1.32 ~ 1.72</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>23.18</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3681,8 +3709,12 @@
           <t>1.23 ~ 1.63</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>14.18</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -5370,7 +5402,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>5.84</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -6202,66 +6236,62 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26秦皇城投PPN002</t>
+          <t>G26垦利2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
-        </is>
-      </c>
-      <c r="C27" s="3"/>
+          <t>09-14 19:00</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>283998.SH</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>1.7</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>2.20 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>108.71</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>25秦发02</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>3.47Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8618</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2.0900/1.8500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>C- 12.37</t>
-        </is>
-      </c>
+          <t>东营市垦利区城市发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P27" s="3"/>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -6269,7 +6299,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6282,20 +6312,16 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U27" s="4" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.59%~2.69%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6306,23 +6332,27 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>河北省-秦皇岛市</t>
+          <t>山东省-东营市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次发行6.50亿元,全部用于偿还到期债务融资工具本金；本期发行5.00亿元,全部用于偿还到期债务融资工具本金[25秦皇城投CP002,24秦皇城投PPN001]</t>
+          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,中国民生银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3"/>
+          <t>粤开证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6332,12 +6362,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6347,22 +6377,18 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2033-09-15</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN27" s="3" t="inlineStr">
@@ -6372,14 +6398,10 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP27" s="3"/>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -6397,7 +6419,7 @@
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6407,7 +6429,7 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
@@ -6425,24 +6447,22 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN017</t>
+          <t>G26垦利1(取消发行)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-14 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683620.IB</t>
+          <t>DY283997.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6451,53 +6471,39 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.93</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>26晋能煤业MTN016</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>4.98Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9747</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.9700/1.9500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>B- 36.31</t>
-        </is>
-      </c>
+          <t>东营市垦利区城市发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P28" s="3"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -6505,7 +6511,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6522,39 +6528,43 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>2.29%~2.39%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>山东省-东营市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3"/>
+          <t>粤开证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6564,17 +6574,17 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十七期中期票据</t>
+          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
@@ -6585,7 +6595,7 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6603,29 +6613,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP28" s="3"/>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6635,7 +6641,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6658,7 +6664,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业GN011(科创债)</t>
+          <t>26秦皇城投PPN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6666,62 +6672,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>132680096.IB</t>
-        </is>
-      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>55.09</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业MTN007(科创债)</t>
+          <t>25秦发02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.74Y</t>
+          <t>3.47Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.1647</t>
+          <t>1.8618</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/2.1800</t>
+          <t>2.0900/1.8500</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司</t>
+          <t>秦皇岛城市发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.31</t>
+          <t>C- 12.37</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6731,7 +6735,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6745,55 +6749,51 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.1</v>
+        <v>5.96</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.0</v>
+        <v>1.6</v>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>河北省-秦皇岛市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>华友钴业本期绿色科技创新债券拟发行规模为10.00亿元人民币,募集资金全部用于置换发行人下属公司三个月内用于废旧动力蓄电池及其拆解物回收,以及用于电池级锂盐产品制造项目原材料采购的采购支出,其中22,801.28万元用于置换发行人下属公司衢州华友资源再生科技有限公司三个月内废旧动力蓄电池及其拆解物回收的采购支出;77,198.72万元用于置换发行人下属子公司广西华友锂业有限公司三个月内用于电池级锂盐产品制造项目原材料采购的采购支出</t>
+          <t>本次发行6.50亿元,全部用于偿还到期债务融资工具本金；本期发行5.00亿元,全部用于偿还到期债务融资工具本金[25秦皇城投CP002,24秦皇城投PPN001]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,招商银行股份有限公司,中银国际证券股份有限公司,中国银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6803,20 +6803,24 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司2026年度第十一期绿色科技创新债券</t>
+          <t>秦皇岛城市发展投资控股集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2028-09-15</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -6824,7 +6828,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6834,32 +6838,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6888,13 +6892,13 @@
         </is>
       </c>
       <c r="AZ29" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26招商租赁SCP008</t>
+          <t>26晋能煤业MTN017</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6904,60 +6908,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682249.IB</t>
+          <t>102683620.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.50 ~ 1.93</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>51.11</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25招商租赁MTN001(绿色)</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>286D</t>
+          <t>4.98Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5330</t>
+          <t>1.9747</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/1.9500</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>招商局融资租赁有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 24.06</t>
+          <t>B- 36.31</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6967,7 +6975,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6980,20 +6988,16 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7004,28 +7008,28 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,期限为269天。根据发行人资金需求计划,本期超短期融资券募集资金拟用于偿还发行人到期债务融资工具[26招商租赁SCP001]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -7035,7 +7039,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>招商局融资租赁有限公司2026年度第八期超短期融资券</t>
+          <t>晋能控股煤业集团有限公司2026年度第十七期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7045,7 +7049,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-06-11</t>
+          <t>2031-09-15</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7066,7 +7070,7 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
@@ -7076,22 +7080,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7124,7 +7128,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP019</t>
+          <t>26华友钴业GN011(科创债)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7134,60 +7138,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>012682246.IB</t>
+          <t>132680096.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>95.64</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26华友钴业MTN007(科创债)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>1.74Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>2.1647</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/2.1800</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>浙江华友钴业股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.41</t>
+          <t>C+ 33.31</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7211,19 +7219,19 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.08</v>
+        <v>1.1</v>
       </c>
       <c r="V31" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7231,31 +7239,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>华友钴业本期绿色科技创新债券拟发行规模为10.00亿元人民币,募集资金全部用于置换发行人下属公司三个月内用于废旧动力蓄电池及其拆解物回收,以及用于电池级锂盐产品制造项目原材料采购的采购支出,其中22,801.28万元用于置换发行人下属公司衢州华友资源再生科技有限公司三个月内废旧动力蓄电池及其拆解物回收的采购支出;77,198.72万元用于置换发行人下属子公司广西华友锂业有限公司三个月内用于电池级锂盐产品制造项目原材料采购的采购支出</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,招商银行股份有限公司,中银国际证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7265,7 +7277,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十九期超短期融资券</t>
+          <t>浙江华友钴业股份有限公司2026年度第十一期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7275,7 +7287,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2028-09-15</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7306,22 +7318,22 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7349,12 +7361,14 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ31" s="3"/>
+      <c r="AZ31" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26深能源SCP003</t>
+          <t>26招商租赁SCP008</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7364,60 +7378,64 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>012682244.IB</t>
+          <t>012682249.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>18.18</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26深能源SCP001</t>
+          <t>25招商租赁MTN001(绿色)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>95D</t>
+          <t>286D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.4800</t>
+          <t>1.5330</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司</t>
+          <t>招商局融资租赁有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 46.10</t>
+          <t>C- 24.06</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7441,19 +7459,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7464,17 +7482,17 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金10亿元,其中4.2亿元拟用于偿还发行人有息负债本息,5.8亿元拟用于发行人本部及子公司补充流动资金。</t>
+          <t>本期超短期融资券发行金额5亿元,期限为269天。根据发行人资金需求计划,本期超短期融资券募集资金拟用于偿还发行人到期债务融资工具[26招商租赁SCP001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信银行股份有限公司</t>
+          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7485,7 +7503,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7495,7 +7513,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司2026年度第三期超短期融资券</t>
+          <t>招商局融资租赁有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7505,7 +7523,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-06-11</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7526,32 +7544,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7584,7 +7602,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26大唐租赁SCP007</t>
+          <t>26苏农垦SCP019</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7594,60 +7612,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>012682245.IB</t>
+          <t>012682246.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>22.01</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26大唐租赁SCP006</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>67D</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5158</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.4900</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 36.58</t>
+          <t>C+ 34.41</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7671,14 +7693,14 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="V33" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
@@ -7694,17 +7716,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为基础发行规模0元，发行金额上限10亿元，用于偿还有息负债[26大唐租赁SCP003]</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7715,7 +7737,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7725,7 +7747,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>江苏省农垦集团有限公司2026年度第十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7735,7 +7757,7 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7756,32 +7778,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7814,7 +7836,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26河南发电SCP002</t>
+          <t>26深能源SCP003</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7824,60 +7846,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682243.IB</t>
+          <t>012682244.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.51Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.20 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>15.01</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25河南发电MTN003</t>
+          <t>26深能源SCP001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>332D</t>
+          <t>95D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.5393</t>
+          <t>1.4800</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>大唐河南发电有限公司</t>
+          <t>深圳能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.89</t>
+          <t>B- 46.10</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7900,16 +7926,20 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7920,17 +7950,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期发行超短期融资券5亿元,拟全部用于偿还发行人有息债务[26河南发电SCP001]</t>
+          <t>本期超短期融资券募集资金10亿元,其中4.2亿元拟用于偿还发行人有息负债本息,5.8亿元拟用于发行人本部及子公司补充流动资金。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7941,7 +7971,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -7951,7 +7981,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>大唐河南发电有限公司2026年度第二期超短期融资券</t>
+          <t>深圳能源集团股份有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7961,14 +7991,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -7991,7 +8017,7 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -8001,12 +8027,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -8044,7 +8070,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP003</t>
+          <t>26大唐租赁SCP007</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8054,60 +8080,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682251.IB</t>
+          <t>012682245.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+          <t>1.31 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>23.01</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP002</t>
+          <t>26大唐租赁SCP006</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>266D</t>
+          <t>67D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.5303</t>
+          <t>1.5158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5300</t>
+          <t>--/1.4900</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 18.59</t>
+          <t>B- 36.58</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8131,47 +8161,43 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.86</v>
+        <v>1.37</v>
       </c>
       <c r="V35" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期超短期融资券发行金额为基础发行规模0元，发行金额上限10亿元，用于偿还有息负债[26大唐租赁SCP003]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>超短期融资券(SCP)</t>
@@ -8179,7 +8205,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8189,7 +8215,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期超短期融资券</t>
+          <t>大唐融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8199,14 +8225,10 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -8224,32 +8246,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8259,7 +8281,7 @@
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
@@ -8282,7 +8304,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26福州新发MTN002</t>
+          <t>26河南发电SCP002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8292,60 +8314,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683623.IB</t>
+          <t>012682243.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.51Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>21.53</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24福州新发MTN002</t>
+          <t>25河南发电MTN003</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>332D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6696</t>
+          <t>1.5393</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>福州新区开发投资集团有限公司</t>
+          <t>大唐河南发电有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.14</t>
+          <t>D+ 8.89</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8355,7 +8381,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-14 10:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8368,20 +8394,16 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U36" s="4" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>2.04</v>
-      </c>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8392,28 +8414,28 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币6.00亿元,拟用于归还到期债券[21福州新发MTN005]</t>
+          <t>本期发行超短期融资券5亿元,拟全部用于偿还发行人有息债务[26河南发电SCP001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8423,7 +8445,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>福州新区开发投资集团有限公司2026年度第二期中期票据</t>
+          <t>大唐河南发电有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8433,7 +8455,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t>2027-03-20</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
@@ -8458,32 +8480,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8511,79 +8533,79 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26亚新煤层气GT02</t>
+          <t>26南京公路SCP003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-14 19:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>520465.SZ</t>
+          <t>012682251.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>43.11</v>
+        <v>18.18</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26亚新煤层气GT01</t>
+          <t>26南京公路SCP002</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.60Y</t>
+          <t>266D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.0923</t>
+          <t>1.5303</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/2.0800</t>
+          <t>1.5400/1.5300</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>新疆亚新煤层气投资开发(集团)有限责任公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 18.59</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8593,7 +8615,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-14 15:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8603,19 +8625,23 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8626,27 +8652,27 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金不超过3.00亿元(含),扣除发行费用后,拟全部用于置换本期债券发行前三个月在低碳转型领域自有资金的支出</t>
+          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>湘财证券股份有限公司</t>
+          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3" t="inlineStr">
         <is>
-          <t>陕西信用增进投资股份有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8656,28 +8682,32 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>新疆亚新煤层气投资开发(集团)有限责任公司2026年面向专业投资者非公开发行低碳转型公司债券(第二期)</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8687,37 +8717,37 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>油气开采</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8750,119 +8780,137 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>G26垦利1</t>
+          <t>26福州新发MTN002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-14 19:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283997.SH</t>
+          <t>102683623.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>44.09</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>24福州新发MTN002</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2.61Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.6696</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>1.6900/1.6600</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>福州新区开发投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>D+ 9.14</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-14 10:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>东营市垦利区城市发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>09-14 15:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>2.04</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.29%~2.39%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>山东省-东营市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
+          <t>本期中期票据发行金额为人民币6.00亿元,拟用于归还到期债券[21福州新发MTN005]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>粤开证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>湖南财鑫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8872,74 +8920,82 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种一)</t>
+          <t>福州新区开发投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -8957,69 +9013,79 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ38" s="3"/>
+      <c r="AZ38" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26吉安井开PPN001A</t>
+          <t>26亚新煤层气GT02</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
-        </is>
-      </c>
-      <c r="C39" s="3"/>
+          <t>09-14 19:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>520465.SZ</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.8</v>
+        <v>3.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+          <t>1.80 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>43.11</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25吉安井开PPN001</t>
+          <t>26亚新煤层气GT01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.11Y+2.00Y</t>
+          <t>4.60Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.0555</t>
+          <t>2.0923</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/2.0800</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
+          <t>新疆亚新煤层气投资开发(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 19.58</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9029,7 +9095,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9039,50 +9105,50 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.18</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
+          <t>本期公司债券募集资金不超过3.00亿元(含),扣除发行费用后,拟全部用于置换本期债券发行前三个月在低碳转型领域自有资金的支出</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3"/>
+          <t>湘财证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>陕西信用增进投资股份有限公司</t>
+        </is>
+      </c>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9092,12 +9158,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种一)</t>
+          <t>新疆亚新煤层气投资开发(集团)有限责任公司2026年面向专业投资者非公开发行低碳转型公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9107,68 +9173,68 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
+          <t>2031-09-16</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>油气开采</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9181,14 +9247,12 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ39" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ39" s="3"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26吉安井开PPN001B</t>
+          <t>26吉安井开PPN001A</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9199,7 +9263,7 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -9208,14 +9272,18 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>58.11</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -9269,10 +9337,10 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2.78</v>
+        <v>4.89</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>3.6</v>
+        <v>1.18</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -9281,7 +9349,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9323,7 +9391,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9384,7 +9452,7 @@
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9394,7 +9462,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9408,13 +9476,13 @@
         </is>
       </c>
       <c r="AZ40" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN003</t>
+          <t>26吉安井开PPN001B</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9422,62 +9490,60 @@
           <t>09-14 18:00</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>102683617.IB</t>
-        </is>
-      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>92.11</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN002</t>
+          <t>25吉安井开PPN001</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>2.11Y+2.00Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>2.0555</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7500</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 39.41</t>
+          <t>C- 19.58</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9487,7 +9553,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9501,55 +9567,51 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,中国银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9559,24 +9621,20 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司2026年度第三期中期票据</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -9594,32 +9652,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9634,12 +9692,12 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY41" s="3" t="inlineStr">
@@ -9647,77 +9705,81 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26融运01</t>
+          <t>26中冶MTN003</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-14 19:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>284032.SH</t>
+          <t>102683617.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>72.11</v>
+        <v>51.09</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25融运01</t>
+          <t>26中冶MTN002</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>2.95Y+N</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.8834</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.7600/1.7500</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>新乡新融资产运营有限公司</t>
+          <t>中国冶金科工股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B- 39.41</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9727,7 +9789,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-14 16:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9737,141 +9799,149 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司,中国银行股份有限公司,中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>中国冶金科工股份有限公司2026年度第三期中期票据</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK42" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t>1.84%~1.94%</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3" t="inlineStr">
-        <is>
-          <t>河南省-新乡市</t>
-        </is>
-      </c>
-      <c r="AB42" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司到期有息债务。</t>
-        </is>
-      </c>
-      <c r="AC42" s="3" t="inlineStr">
-        <is>
-          <t>华泰联合证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
-      <c r="AE42" s="3" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="AF42" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AG42" s="3" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>新乡新融资产运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="AI42" s="3" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="AJ42" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-16</t>
-        </is>
-      </c>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="3" t="inlineStr">
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>综合建筑施工</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>综合建筑施工</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY42" s="3" t="inlineStr">
@@ -9884,70 +9954,72 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26平安点创SCP004</t>
+          <t>26融运01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-14 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>012682248.IB</t>
+          <t>284032.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>72.11</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26平安点创MTN003</t>
+          <t>25融运01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>276D</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7030</t>
+          <t>1.8834</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司</t>
+          <t>新乡新融资产运营有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.36</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9957,7 +10029,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 16:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9967,121 +10039,121 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>1.09</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.70%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元。其中3亿元拟用于偿还发行人即将到期的债务融资工具，1亿元拟用于偿还发行人的银行借款。[25平安点创SCP006]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司到期有息债务。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3"/>
+          <t>华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司2026年度第四期超短期融资券</t>
+          <t>新乡新融资产运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2031-09-16</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10091,7 +10163,7 @@
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
@@ -10109,64 +10181,64 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ43" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ43" s="3"/>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26GTHTS2</t>
+          <t>26平安点创SCP004</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>09-14 19:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>246074.SH</t>
+          <t>012682248.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.75Y</t>
+          <t>0.7Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>3.9</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.00 ~ 2.00</t>
+          <t>1.35 ~ 1.70</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>30.18</v>
+        <v>50.18</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25GTHT03</t>
+          <t>26平安点创MTN003</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>273D</t>
+          <t>276D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.4890</t>
+          <t>1.7030</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -10176,12 +10248,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>平安点创国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>A- 65.30</t>
+          <t>D+ 9.36</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10191,7 +10263,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-14 15:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10201,19 +10273,23 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>1.09</v>
+      </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.66%~1.70%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10221,11 +10297,7 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+      <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>上海市</t>
@@ -10233,33 +10305,33 @@
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金100亿元拟用于偿还或置换到期公司债券本金。[24国君G2,23国君G8,23海通15,21海通09,23国君10]</t>
+          <t>发行人本期超短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元。其中3亿元拟用于偿还发行人即将到期的债务融资工具，1亿元拟用于偿还发行人的银行借款。[25平安点创SCP006]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,国投证券股份有限公司,东方证券股份有限公司,招商证券股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第二期)</t>
+          <t>平安点创国际融资租赁有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10269,86 +10341,88 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2027-06-16</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY44" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AO44" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV44" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW44" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX44" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AZ44" s="3"/>
+      <c r="AZ44" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26工业03</t>
+          <t>26GTHTS2</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10358,47 +10432,47 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>283975.SH</t>
+          <t>246074.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.75Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>56.11</v>
+        <v>30.18</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26工业02</t>
+          <t>25GTHT03</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>273D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.9349</t>
+          <t>1.4890</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10408,12 +10482,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>济南工业投资控股集团有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.88</t>
+          <t>A- 65.30</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10436,16 +10510,18 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U45" s="3"/>
+      <c r="U45" s="4" t="n">
+        <v>3.53</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10453,26 +10529,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z45" s="3"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不超过8亿元(含8亿元)用于偿还有息债务,不超过7亿元(含7亿元)用于向子公司济南工控资本有限公司权益出资</t>
+          <t>本期债券募集资金100亿元拟用于偿还或置换到期公司债券本金。[24国君G2,23国君G8,23海通15,21海通09,23国君10]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,申万宏源证券有限公司</t>
+          <t>申万宏源证券有限公司,国投证券股份有限公司,东方证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10487,17 +10567,17 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>济南工业投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>国泰海通证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
+          <t>2027-06-16</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10508,7 +10588,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10518,32 +10598,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10576,7 +10656,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>G26垦利2</t>
+          <t>26工业03</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10586,106 +10666,118 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>283998.SH</t>
+          <t>283975.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.7</v>
+        <v>15.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.70 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>56.11</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>26工业02</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>4.95Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.9349</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>济南工业投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>C+ 30.88</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>东营市垦利区城市发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>09-14 15:00</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>2.59%~2.69%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>山东省-东营市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过3.40亿元，募集资金扣除发行费用后，全部用于东营市垦利区光储充绿能建设项目</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不超过8亿元(含8亿元)用于偿还有息债务,不超过7亿元(含7亿元)用于向子公司济南工控资本有限公司权益出资</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>粤开证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>湖南财鑫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>五矿证券有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10703,7 +10795,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>东营市垦利区城市发展集团有限公司2026年面向专业投资者非公开发行绿色公司债券(第一期)(品种二)</t>
+          <t>济南工业投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10713,7 +10805,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2033-09-15</t>
+          <t>2031-09-16</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10729,7 +10821,7 @@
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
@@ -10737,7 +10829,11 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP46" s="3"/>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -10745,12 +10841,12 @@
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
@@ -10765,7 +10861,7 @@
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
@@ -11108,7 +11204,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U48" s="3"/>
+      <c r="U48" s="4" t="n">
+        <v>4.38</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
@@ -11336,7 +11434,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U49" s="3"/>
+      <c r="U49" s="4" t="n">
+        <v>3.57</v>
+      </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-09-14.xlsx
+++ b/data/credit_bond_all_2026-09-14.xlsx
@@ -721,8 +721,12 @@
           <t>1.35 ~ 1.95</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>24.09</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -1187,8 +1191,12 @@
           <t>1.40 ~ 1.79</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>36.35</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -1244,7 +1252,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>1.16</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1474,7 +1484,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>0.81</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
@@ -3961,7 +3973,9 @@
       <c r="E17" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4" t="n">
+        <v>3.4</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>2.20 ~ 3.20</t>
@@ -4020,7 +4034,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>2.94</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
@@ -6815,7 +6831,7 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.38</v>
+        <v>5.3833</v>
       </c>
       <c r="V29" s="4" t="n">
         <v>2.04</v>
@@ -11689,7 +11705,7 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="V50" s="4" t="n">
         <v>1.0</v>
@@ -12400,7 +12416,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U53" s="3"/>
+      <c r="U53" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
@@ -12835,7 +12853,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -12869,7 +12887,7 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>2.86</v>
+        <v>2.8667</v>
       </c>
       <c r="V55" s="4" t="n">
         <v>1.0</v>

--- a/data/credit_bond_all_2026-09-14.xlsx
+++ b/data/credit_bond_all_2026-09-14.xlsx
@@ -7035,12 +7035,8 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>58.11</v>
-      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -7096,12 +7092,8 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.18</v>
-      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
           <t>7-</t>

--- a/data/credit_bond_all_2026-09-14.xlsx
+++ b/data/credit_bond_all_2026-09-14.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-17" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-18" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 36.03</t>
+          <t>B- 38.97</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 37.68</t>
+          <t>B- 38.09</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 38.59</t>
+          <t>B- 39.45</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2015,7 +2015,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 11.91</t>
+          <t>C- 12.12</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 43.29</t>
+          <t>B- 42.11</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 37.68</t>
+          <t>B- 38.09</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B 52.60</t>
+          <t>B+ 55.39</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 22.29</t>
+          <t>C- 23.26</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.58</t>
+          <t>C+ 34.65</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>A- 63.12</t>
+          <t>A- 63.76</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4101,7 +4101,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN005</t>
+          <t>26巨石MTN002(科创债)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4184,64 +4184,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683624.IB</t>
+          <t>102683625.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>40.0</v>
+        <v>5.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>40.0</v>
+        <v>5.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.95</t>
+          <t>1.40 ~ 1.79</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>24.09</v>
+        <v>36.35</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN004</t>
+          <t>25巨石MTN007(科创债)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.03Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6542</t>
+          <t>1.6391</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司</t>
+          <t>中国巨石股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.61</t>
+          <t>C 27.78</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4264,18 +4264,20 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>1.16</v>
+      </c>
       <c r="V18" s="4" t="n">
-        <v>1.66</v>
+        <v>1.0</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4286,17 +4288,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
+          <t>发行人本期发行科技创新债券5亿元，用于偿还发行人即将到期的有息负债[26巨石SCP004]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4307,7 +4309,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4317,7 +4319,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司2026年度第五期中期票据</t>
+          <t>中国巨石股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4327,14 +4329,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-16</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -4357,27 +4355,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>其他建材</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>其他建材</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>计算机设备</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4410,74 +4408,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26巨石MTN002(科创债)</t>
+          <t>26山金Y2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-15 18:00</t>
+          <t>09-14 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683625.IB</t>
+          <t>246069.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.79</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>36.35</v>
+        <v>43.11</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25巨石MTN007(科创债)</t>
+          <t>24鲁黄金MTN004(科创票据)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.03Y</t>
+          <t>223D+N</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6391</t>
+          <t>1.5603</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中国巨石股份有限公司</t>
+          <t>山东黄金集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 22.69</t>
+          <t>C- 17.23</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4487,7 +4485,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 16:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4501,19 +4499,17 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.44</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4521,41 +4517,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z19" s="3"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行科技创新债券5亿元，用于偿还发行人即将到期的有息负债[26巨石SCP004]</t>
+          <t>本期公司债券募集资金扣除发行费用后拟用于偿还公司有息债务</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
+          <t>中信证券股份有限公司,东兴证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中国巨石股份有限公司2026年度第二期科技创新债券</t>
+          <t>山东黄金集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4571,7 +4571,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4591,27 +4591,27 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>其他建材</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>其他建材</t>
+          <t>贵金属</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AY19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AZ19" s="3"/>
@@ -4644,7 +4644,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26山金Y2</t>
+          <t>HDGJYK02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4654,64 +4654,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>246069.SH</t>
+          <t>246092.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>17.95</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.0</v>
+        <v>19.9</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>43.11</v>
+        <v>35.64</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24鲁黄金MTN004(科创票据)</t>
+          <t>HDGJYK01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>223D+N</t>
+          <t>1.87Y+N</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5603</t>
+          <t>1.5989</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司</t>
+          <t>华电国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 19.92</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>09-14 16:00</t>
+          <t>09-14 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4735,17 +4735,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.44</v>
+        <v>3.3719</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后拟用于偿还公司有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东兴证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4801,10 +4801,14 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2028-09-16</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4812,7 +4816,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4827,27 +4831,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4867,7 +4871,7 @@
       </c>
       <c r="AX20" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY20" s="3" t="inlineStr">
@@ -4880,7 +4884,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>HDGJYK02</t>
+          <t>HDGJYK03</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4890,34 +4894,34 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>246092.SH</t>
+          <t>246093.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>17.95</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>19.9</v>
+        <v>16.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>35.64</v>
+        <v>39.09</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -4947,7 +4951,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 42.33</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4971,7 +4975,7 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.3719</v>
+        <v>3.9563</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
@@ -4981,7 +4985,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5027,7 +5031,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
+          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5037,12 +5041,12 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2028-09-16</t>
+          <t>2029-09-16</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL21" s="3" t="inlineStr">
@@ -5120,7 +5124,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>HDGJYK03</t>
+          <t>26融运01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5130,64 +5134,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246093.SH</t>
+          <t>284032.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.95</v>
+        <v>8.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>39.09</v>
+        <v>72.11</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>HDGJYK01</t>
+          <t>25融运01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>1.87Y+N</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5989</t>
+          <t>1.8834</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司</t>
+          <t>新乡新融资产运营有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 42.33</t>
+          <t>D+ 8.18</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5197,7 +5201,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-14 15:00</t>
+          <t>09-14 16:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5211,45 +5215,45 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.9563</v>
+        <v>3.84</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司到期有息债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3"/>
+          <t>华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5257,7 +5261,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5267,24 +5271,20 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
+          <t>新乡新融资产运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-16</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5307,27 +5307,27 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY22" s="3" t="inlineStr">
@@ -5360,17 +5360,17 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26融运01</t>
+          <t>26创鸿资产PPN001</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-14 19:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>284032.SH</t>
+          <t>032680525.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -5379,55 +5379,55 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>8.0</v>
+        <v>1.65</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8.0</v>
+        <v>1.65</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>72.11</v>
+        <v>63.11</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25融运01</t>
+          <t>25创鸿06</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>4.25Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8834</t>
+          <t>1.9041</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>新乡新融资产运营有限公司</t>
+          <t>江苏创鸿资产管理有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.18</t>
+          <t>C 25.65</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-14 16:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5447,21 +5447,23 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>2.2545</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.39</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5472,27 +5474,23 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>河南省-新乡市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司到期有息债务。</t>
+          <t>本期定向债务融资工具注册金额1.65亿元,本期发行金额1.65亿元,拟用于偿还发行人有息债务[26创鸿资产SCP001]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5502,12 +5500,12 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>新乡新融资产运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏创鸿资产管理有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5517,63 +5515,63 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
+          <t>2031-09-15</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AO23" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW23" s="3" t="inlineStr">
@@ -5596,7 +5594,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26创鸿资产PPN001</t>
+          <t>26吉安井开PPN001B</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5606,7 +5604,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>032680525.IB</t>
+          <t>032690021.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5615,55 +5613,55 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>63.11</v>
+        <v>92.11</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25创鸿06</t>
+          <t>25吉安井开PPN001</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.25Y</t>
+          <t>2.11Y+2.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.9041</t>
+          <t>2.0555</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>江苏创鸿资产管理有限公司</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 25.65</t>
+          <t>C- 14.81</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5673,7 +5671,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-14 09:00</t>
+          <t>09-14 14:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5687,40 +5685,40 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.2545</v>
+        <v>2.7778</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.39</v>
+        <v>3.6</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具注册金额1.65亿元,本期发行金额1.65亿元,拟用于偿还发行人有息债务[26创鸿资产SCP001]</t>
+          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5741,7 +5739,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>江苏创鸿资产管理有限公司2026年度第一期定向债务融资工具</t>
+          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5772,12 +5770,12 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5797,7 +5795,7 @@
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5825,79 +5823,81 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26吉安井开PPN001B</t>
+          <t>26华为MTN005</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-15 18:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>032690021.IB</t>
+          <t>102683624.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.8</v>
+        <v>40.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.6</v>
+        <v>40.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.35 ~ 1.95</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>92.11</v>
+        <v>24.09</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25吉安井开PPN001</t>
+          <t>26华为MTN004</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.11Y+2.00Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>2.0555</t>
+          <t>1.6542</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司</t>
+          <t>华为投资控股有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 10.92</t>
+          <t>C+ 31.74</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-14 14:00</t>
+          <t>09-14 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5917,55 +5917,55 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.7778</v>
+        <v>3.3375</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.6</v>
+        <v>1.66</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具基础发行规模为0亿元,发行规模上限为3.6亿元,募集资金用于偿还到期的债务融资工具本金。[23吉安井开PPN003]</t>
+          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5975,93 +5975,95 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>吉安市井冈山开发区金庐陵经济发展有限公司2026年度第一期定向债务融资工具(品种二)</t>
+          <t>华为投资控股有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2029-09-16</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>计算机设备</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY25" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW25" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX25" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -6373,7 +6375,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 36.78</t>
+          <t>B- 37.49</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6605,7 +6607,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C+ 32.94</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6839,7 +6841,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 23.68</t>
+          <t>C 25.06</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7069,7 +7071,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 10.92</t>
+          <t>C- 14.81</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7537,7 +7539,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 25.23</t>
+          <t>C- 23.97</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7995,7 +7997,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 19.92</t>
+          <t>C- 17.23</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8227,7 +8229,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D- 2.51</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8457,7 +8459,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 41.83</t>
+          <t>B- 42.65</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8695,7 +8697,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 36.15</t>
+          <t>B- 38.54</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8929,7 +8931,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 22.59</t>
+          <t>C- 24.69</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9395,7 +9397,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.42</t>
+          <t>B- 35.11</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -10107,7 +10109,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 12.00</t>
+          <t>C- 12.50</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10343,7 +10345,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B- 41.85</t>
+          <t>B- 42.78</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10577,7 +10579,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 18.03</t>
+          <t>C- 16.29</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -11293,7 +11295,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 37.15</t>
+          <t>B- 39.28</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11389,7 +11391,7 @@
       </c>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11525,7 +11527,7 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C- 17.13</t>
+          <t>C- 17.57</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11621,7 +11623,7 @@
       </c>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -11761,7 +11763,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.30</t>
+          <t>C+ 34.72</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12083,7 +12085,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -12315,7 +12317,7 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM52" s="3" t="inlineStr">
@@ -12455,7 +12457,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>D- 2.51</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12687,7 +12689,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 25.76</t>
+          <t>C 26.29</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12783,7 +12785,7 @@
       </c>
       <c r="AL54" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM54" s="3" t="inlineStr">
@@ -12923,7 +12925,7 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 23.82</t>
+          <t>C- 23.45</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -13015,7 +13017,7 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM55" s="3" t="inlineStr">
